--- a/demo_alarms.xlsx
+++ b/demo_alarms.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,8 +80,14 @@
       <color rgb="00555555"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -123,6 +129,11 @@
         <fgColor rgb="00F0FFF4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE5E5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -161,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="287">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -644,6 +655,381 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1011,7 +1397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:R58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1128,32 +1514,32 @@
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="137" t="inlineStr">
+      <c r="A3" s="257" t="inlineStr">
         <is>
           <t>ALM-0001</t>
         </is>
       </c>
-      <c r="B3" s="138" t="inlineStr">
+      <c r="B3" s="258" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C3" s="138" t="inlineStr">
+      <c r="C3" s="258" t="inlineStr">
         <is>
           <t>13:50:50</t>
         </is>
       </c>
-      <c r="D3" s="139" t="inlineStr">
+      <c r="D3" s="259" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E3" s="139" t="inlineStr">
+      <c r="E3" s="259" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F3" s="139" t="inlineStr">
+      <c r="F3" s="259" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -1163,33 +1549,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H3" s="138" t="inlineStr">
+      <c r="H3" s="258" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I3" s="138" t="n">
+      <c r="I3" s="258" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="139" t="inlineStr">
+      <c r="J3" s="259" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K3" s="138" t="n">
+      <c r="K3" s="258" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="L3" s="155" t="inlineStr">
+      <c r="L3" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M3" s="141" t="inlineStr">
+      <c r="M3" s="261" t="inlineStr">
         <is>
           <t>ALARM RAISED</t>
         </is>
       </c>
-      <c r="N3" s="138" t="n">
+      <c r="N3" s="258" t="n">
         <v>0</v>
       </c>
       <c r="O3" s="6" t="inlineStr">
@@ -1197,7 +1583,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P3" s="139" t="inlineStr">
+      <c r="P3" s="259" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -1209,32 +1595,32 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="152" t="inlineStr">
+      <c r="A4" s="272" t="inlineStr">
         <is>
           <t>ALM-0001</t>
         </is>
       </c>
-      <c r="B4" s="153" t="inlineStr">
+      <c r="B4" s="273" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C4" s="153" t="inlineStr">
+      <c r="C4" s="273" t="inlineStr">
         <is>
           <t>13:50:50</t>
         </is>
       </c>
-      <c r="D4" s="154" t="inlineStr">
+      <c r="D4" s="274" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E4" s="154" t="inlineStr">
+      <c r="E4" s="274" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F4" s="154" t="inlineStr">
+      <c r="F4" s="274" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -1244,33 +1630,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H4" s="153" t="inlineStr">
+      <c r="H4" s="273" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I4" s="153" t="n">
+      <c r="I4" s="273" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="154" t="inlineStr">
+      <c r="J4" s="274" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K4" s="153" t="n">
+      <c r="K4" s="273" t="n">
         <v>91.5</v>
       </c>
-      <c r="L4" s="155" t="inlineStr">
+      <c r="L4" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M4" s="156" t="inlineStr">
+      <c r="M4" s="276" t="inlineStr">
         <is>
           <t>ALARM ACTIVE</t>
         </is>
       </c>
-      <c r="N4" s="153" t="n">
+      <c r="N4" s="273" t="n">
         <v>0.2</v>
       </c>
       <c r="O4" s="12" t="inlineStr">
@@ -1278,7 +1664,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P4" s="154" t="inlineStr">
+      <c r="P4" s="274" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -1290,32 +1676,32 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="147" t="inlineStr">
+      <c r="A5" s="277" t="inlineStr">
         <is>
           <t>ALM-0001</t>
         </is>
       </c>
-      <c r="B5" s="148" t="inlineStr">
+      <c r="B5" s="278" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C5" s="148" t="inlineStr">
+      <c r="C5" s="278" t="inlineStr">
         <is>
           <t>13:51:00</t>
         </is>
       </c>
-      <c r="D5" s="149" t="inlineStr">
+      <c r="D5" s="279" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E5" s="149" t="inlineStr">
+      <c r="E5" s="279" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F5" s="149" t="inlineStr">
+      <c r="F5" s="279" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -1325,33 +1711,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H5" s="148" t="inlineStr">
+      <c r="H5" s="278" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I5" s="148" t="n">
+      <c r="I5" s="278" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="149" t="inlineStr">
+      <c r="J5" s="279" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K5" s="148" t="n">
+      <c r="K5" s="278" t="n">
         <v>91.59999999999999</v>
       </c>
-      <c r="L5" s="155" t="inlineStr">
+      <c r="L5" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M5" s="151" t="inlineStr">
+      <c r="M5" s="281" t="inlineStr">
         <is>
           <t>ALARM ACTIVE</t>
         </is>
       </c>
-      <c r="N5" s="148" t="n">
+      <c r="N5" s="278" t="n">
         <v>10.3</v>
       </c>
       <c r="O5" s="18" t="inlineStr">
@@ -1359,7 +1745,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P5" s="149" t="inlineStr">
+      <c r="P5" s="279" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -1371,32 +1757,32 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="152" t="inlineStr">
+      <c r="A6" s="272" t="inlineStr">
         <is>
           <t>ALM-0001</t>
         </is>
       </c>
-      <c r="B6" s="153" t="inlineStr">
+      <c r="B6" s="273" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C6" s="153" t="inlineStr">
+      <c r="C6" s="273" t="inlineStr">
         <is>
           <t>13:51:11</t>
         </is>
       </c>
-      <c r="D6" s="154" t="inlineStr">
+      <c r="D6" s="274" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E6" s="154" t="inlineStr">
+      <c r="E6" s="274" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F6" s="154" t="inlineStr">
+      <c r="F6" s="274" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -1406,33 +1792,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H6" s="153" t="inlineStr">
+      <c r="H6" s="273" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I6" s="153" t="n">
+      <c r="I6" s="273" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="154" t="inlineStr">
+      <c r="J6" s="274" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K6" s="153" t="n">
+      <c r="K6" s="273" t="n">
         <v>70.09999999999999</v>
       </c>
-      <c r="L6" s="155" t="inlineStr">
+      <c r="L6" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M6" s="156" t="inlineStr">
+      <c r="M6" s="276" t="inlineStr">
         <is>
           <t>ALARM ACTIVE</t>
         </is>
       </c>
-      <c r="N6" s="153" t="n">
+      <c r="N6" s="273" t="n">
         <v>20.4</v>
       </c>
       <c r="O6" s="12" t="inlineStr">
@@ -1440,7 +1826,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P6" s="154" t="inlineStr">
+      <c r="P6" s="274" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -1452,32 +1838,32 @@
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="147" t="inlineStr">
+      <c r="A7" s="277" t="inlineStr">
         <is>
           <t>ALM-0001</t>
         </is>
       </c>
-      <c r="B7" s="148" t="inlineStr">
+      <c r="B7" s="278" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C7" s="148" t="inlineStr">
+      <c r="C7" s="278" t="inlineStr">
         <is>
           <t>13:51:21</t>
         </is>
       </c>
-      <c r="D7" s="149" t="inlineStr">
+      <c r="D7" s="279" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E7" s="149" t="inlineStr">
+      <c r="E7" s="279" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F7" s="149" t="inlineStr">
+      <c r="F7" s="279" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -1487,33 +1873,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H7" s="148" t="inlineStr">
+      <c r="H7" s="278" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I7" s="148" t="n">
+      <c r="I7" s="278" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="149" t="inlineStr">
+      <c r="J7" s="279" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K7" s="148" t="n">
+      <c r="K7" s="278" t="n">
         <v>80.7</v>
       </c>
-      <c r="L7" s="155" t="inlineStr">
+      <c r="L7" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M7" s="151" t="inlineStr">
+      <c r="M7" s="281" t="inlineStr">
         <is>
           <t>ALARM ACTIVE</t>
         </is>
       </c>
-      <c r="N7" s="148" t="n">
+      <c r="N7" s="278" t="n">
         <v>30.5</v>
       </c>
       <c r="O7" s="18" t="inlineStr">
@@ -1521,7 +1907,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P7" s="149" t="inlineStr">
+      <c r="P7" s="279" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -1533,32 +1919,32 @@
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="117" t="inlineStr">
+      <c r="A8" s="252" t="inlineStr">
         <is>
           <t>ALM-0001</t>
         </is>
       </c>
-      <c r="B8" s="118" t="inlineStr">
+      <c r="B8" s="253" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C8" s="118" t="inlineStr">
+      <c r="C8" s="253" t="inlineStr">
         <is>
           <t>13:51:28</t>
         </is>
       </c>
-      <c r="D8" s="119" t="inlineStr">
+      <c r="D8" s="254" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E8" s="119" t="inlineStr">
+      <c r="E8" s="254" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F8" s="119" t="inlineStr">
+      <c r="F8" s="254" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -1568,33 +1954,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H8" s="118" t="inlineStr">
+      <c r="H8" s="253" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I8" s="118" t="n">
+      <c r="I8" s="253" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="119" t="inlineStr">
+      <c r="J8" s="254" t="inlineStr">
         <is>
           <t>CLEAR</t>
         </is>
       </c>
-      <c r="K8" s="118" t="n">
+      <c r="K8" s="253" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="155" t="inlineStr">
+      <c r="L8" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M8" s="121" t="inlineStr">
+      <c r="M8" s="256" t="inlineStr">
         <is>
           <t>ALARM CLEARED</t>
         </is>
       </c>
-      <c r="N8" s="118" t="n">
+      <c r="N8" s="253" t="n">
         <v>38</v>
       </c>
       <c r="O8" s="34" t="inlineStr">
@@ -1602,7 +1988,7 @@
           <t>NO ACTION REQUIRED</t>
         </is>
       </c>
-      <c r="P8" s="119" t="inlineStr">
+      <c r="P8" s="254" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -1614,32 +2000,32 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="137" t="inlineStr">
+      <c r="A9" s="257" t="inlineStr">
         <is>
           <t>ALM-0002</t>
         </is>
       </c>
-      <c r="B9" s="138" t="inlineStr">
+      <c r="B9" s="258" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C9" s="138" t="inlineStr">
+      <c r="C9" s="258" t="inlineStr">
         <is>
           <t>13:51:29</t>
         </is>
       </c>
-      <c r="D9" s="139" t="inlineStr">
+      <c r="D9" s="259" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E9" s="139" t="inlineStr">
+      <c r="E9" s="259" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F9" s="139" t="inlineStr">
+      <c r="F9" s="259" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -1649,33 +2035,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H9" s="138" t="inlineStr">
+      <c r="H9" s="258" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I9" s="138" t="n">
+      <c r="I9" s="258" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="139" t="inlineStr">
+      <c r="J9" s="259" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K9" s="138" t="n">
+      <c r="K9" s="258" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="L9" s="155" t="inlineStr">
+      <c r="L9" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M9" s="141" t="inlineStr">
+      <c r="M9" s="261" t="inlineStr">
         <is>
           <t>ALARM RAISED</t>
         </is>
       </c>
-      <c r="N9" s="138" t="n">
+      <c r="N9" s="258" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="6" t="inlineStr">
@@ -1683,7 +2069,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P9" s="139" t="inlineStr">
+      <c r="P9" s="259" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -1695,32 +2081,32 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="152" t="inlineStr">
+      <c r="A10" s="272" t="inlineStr">
         <is>
           <t>ALM-0002</t>
         </is>
       </c>
-      <c r="B10" s="153" t="inlineStr">
+      <c r="B10" s="273" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C10" s="153" t="inlineStr">
+      <c r="C10" s="273" t="inlineStr">
         <is>
           <t>13:51:29</t>
         </is>
       </c>
-      <c r="D10" s="154" t="inlineStr">
+      <c r="D10" s="274" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E10" s="154" t="inlineStr">
+      <c r="E10" s="274" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F10" s="154" t="inlineStr">
+      <c r="F10" s="274" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -1730,33 +2116,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H10" s="153" t="inlineStr">
+      <c r="H10" s="273" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I10" s="153" t="n">
+      <c r="I10" s="273" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="154" t="inlineStr">
+      <c r="J10" s="274" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K10" s="153" t="n">
+      <c r="K10" s="273" t="n">
         <v>74</v>
       </c>
-      <c r="L10" s="155" t="inlineStr">
+      <c r="L10" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M10" s="156" t="inlineStr">
+      <c r="M10" s="276" t="inlineStr">
         <is>
           <t>ALARM ACTIVE</t>
         </is>
       </c>
-      <c r="N10" s="153" t="n">
+      <c r="N10" s="273" t="n">
         <v>0.2</v>
       </c>
       <c r="O10" s="12" t="inlineStr">
@@ -1764,7 +2150,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P10" s="154" t="inlineStr">
+      <c r="P10" s="274" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -1776,32 +2162,32 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="147" t="inlineStr">
+      <c r="A11" s="277" t="inlineStr">
         <is>
           <t>ALM-0002</t>
         </is>
       </c>
-      <c r="B11" s="148" t="inlineStr">
+      <c r="B11" s="278" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C11" s="148" t="inlineStr">
+      <c r="C11" s="278" t="inlineStr">
         <is>
           <t>13:51:39</t>
         </is>
       </c>
-      <c r="D11" s="149" t="inlineStr">
+      <c r="D11" s="279" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E11" s="149" t="inlineStr">
+      <c r="E11" s="279" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F11" s="149" t="inlineStr">
+      <c r="F11" s="279" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -1811,33 +2197,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H11" s="148" t="inlineStr">
+      <c r="H11" s="278" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I11" s="148" t="n">
+      <c r="I11" s="278" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="149" t="inlineStr">
+      <c r="J11" s="279" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K11" s="148" t="n">
+      <c r="K11" s="278" t="n">
         <v>85.2</v>
       </c>
-      <c r="L11" s="155" t="inlineStr">
+      <c r="L11" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M11" s="151" t="inlineStr">
+      <c r="M11" s="281" t="inlineStr">
         <is>
           <t>ALARM ACTIVE</t>
         </is>
       </c>
-      <c r="N11" s="148" t="n">
+      <c r="N11" s="278" t="n">
         <v>10.3</v>
       </c>
       <c r="O11" s="18" t="inlineStr">
@@ -1845,7 +2231,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P11" s="149" t="inlineStr">
+      <c r="P11" s="279" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -1857,32 +2243,32 @@
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="117" t="inlineStr">
+      <c r="A12" s="252" t="inlineStr">
         <is>
           <t>ALM-0002</t>
         </is>
       </c>
-      <c r="B12" s="118" t="inlineStr">
+      <c r="B12" s="253" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C12" s="118" t="inlineStr">
+      <c r="C12" s="253" t="inlineStr">
         <is>
           <t>13:51:48</t>
         </is>
       </c>
-      <c r="D12" s="119" t="inlineStr">
+      <c r="D12" s="254" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E12" s="119" t="inlineStr">
+      <c r="E12" s="254" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F12" s="119" t="inlineStr">
+      <c r="F12" s="254" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -1892,33 +2278,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H12" s="118" t="inlineStr">
+      <c r="H12" s="253" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I12" s="118" t="n">
+      <c r="I12" s="253" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="119" t="inlineStr">
+      <c r="J12" s="254" t="inlineStr">
         <is>
           <t>CLEAR</t>
         </is>
       </c>
-      <c r="K12" s="118" t="n">
+      <c r="K12" s="253" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="155" t="inlineStr">
+      <c r="L12" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M12" s="121" t="inlineStr">
+      <c r="M12" s="256" t="inlineStr">
         <is>
           <t>ALARM CLEARED</t>
         </is>
       </c>
-      <c r="N12" s="118" t="n">
+      <c r="N12" s="253" t="n">
         <v>19.2</v>
       </c>
       <c r="O12" s="34" t="inlineStr">
@@ -1926,7 +2312,7 @@
           <t>NO ACTION REQUIRED</t>
         </is>
       </c>
-      <c r="P12" s="119" t="inlineStr">
+      <c r="P12" s="254" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -1938,32 +2324,32 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="137" t="inlineStr">
+      <c r="A13" s="257" t="inlineStr">
         <is>
           <t>ALM-0003</t>
         </is>
       </c>
-      <c r="B13" s="138" t="inlineStr">
+      <c r="B13" s="258" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C13" s="138" t="inlineStr">
+      <c r="C13" s="258" t="inlineStr">
         <is>
           <t>13:51:48</t>
         </is>
       </c>
-      <c r="D13" s="139" t="inlineStr">
+      <c r="D13" s="259" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E13" s="139" t="inlineStr">
+      <c r="E13" s="259" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F13" s="139" t="inlineStr">
+      <c r="F13" s="259" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -1973,33 +2359,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H13" s="138" t="inlineStr">
+      <c r="H13" s="258" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I13" s="138" t="n">
+      <c r="I13" s="258" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="139" t="inlineStr">
+      <c r="J13" s="259" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K13" s="138" t="n">
+      <c r="K13" s="258" t="n">
         <v>59.3</v>
       </c>
-      <c r="L13" s="155" t="inlineStr">
+      <c r="L13" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M13" s="141" t="inlineStr">
+      <c r="M13" s="261" t="inlineStr">
         <is>
           <t>ALARM RAISED</t>
         </is>
       </c>
-      <c r="N13" s="138" t="n">
+      <c r="N13" s="258" t="n">
         <v>0</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
@@ -2007,7 +2393,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P13" s="139" t="inlineStr">
+      <c r="P13" s="259" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -2019,32 +2405,32 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="152" t="inlineStr">
+      <c r="A14" s="272" t="inlineStr">
         <is>
           <t>ALM-0003</t>
         </is>
       </c>
-      <c r="B14" s="153" t="inlineStr">
+      <c r="B14" s="273" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C14" s="153" t="inlineStr">
+      <c r="C14" s="273" t="inlineStr">
         <is>
           <t>13:51:48</t>
         </is>
       </c>
-      <c r="D14" s="154" t="inlineStr">
+      <c r="D14" s="274" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E14" s="154" t="inlineStr">
+      <c r="E14" s="274" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F14" s="154" t="inlineStr">
+      <c r="F14" s="274" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -2054,33 +2440,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H14" s="153" t="inlineStr">
+      <c r="H14" s="273" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I14" s="153" t="n">
+      <c r="I14" s="273" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="154" t="inlineStr">
+      <c r="J14" s="274" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K14" s="153" t="n">
+      <c r="K14" s="273" t="n">
         <v>67.09999999999999</v>
       </c>
-      <c r="L14" s="155" t="inlineStr">
+      <c r="L14" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M14" s="156" t="inlineStr">
+      <c r="M14" s="276" t="inlineStr">
         <is>
           <t>ALARM ACTIVE</t>
         </is>
       </c>
-      <c r="N14" s="153" t="n">
+      <c r="N14" s="273" t="n">
         <v>0.2</v>
       </c>
       <c r="O14" s="12" t="inlineStr">
@@ -2088,7 +2474,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P14" s="154" t="inlineStr">
+      <c r="P14" s="274" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -2100,32 +2486,32 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="117" t="inlineStr">
+      <c r="A15" s="252" t="inlineStr">
         <is>
           <t>ALM-0003</t>
         </is>
       </c>
-      <c r="B15" s="118" t="inlineStr">
+      <c r="B15" s="253" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C15" s="118" t="inlineStr">
+      <c r="C15" s="253" t="inlineStr">
         <is>
           <t>13:51:49</t>
         </is>
       </c>
-      <c r="D15" s="119" t="inlineStr">
+      <c r="D15" s="254" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E15" s="119" t="inlineStr">
+      <c r="E15" s="254" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F15" s="119" t="inlineStr">
+      <c r="F15" s="254" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -2135,33 +2521,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H15" s="118" t="inlineStr">
+      <c r="H15" s="253" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I15" s="118" t="n">
+      <c r="I15" s="253" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="119" t="inlineStr">
+      <c r="J15" s="254" t="inlineStr">
         <is>
           <t>CLEAR</t>
         </is>
       </c>
-      <c r="K15" s="118" t="n">
+      <c r="K15" s="253" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="155" t="inlineStr">
+      <c r="L15" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M15" s="121" t="inlineStr">
+      <c r="M15" s="256" t="inlineStr">
         <is>
           <t>ALARM CLEARED</t>
         </is>
       </c>
-      <c r="N15" s="118" t="n">
+      <c r="N15" s="253" t="n">
         <v>0.9</v>
       </c>
       <c r="O15" s="34" t="inlineStr">
@@ -2169,7 +2555,7 @@
           <t>NO ACTION REQUIRED</t>
         </is>
       </c>
-      <c r="P15" s="119" t="inlineStr">
+      <c r="P15" s="254" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -2181,32 +2567,32 @@
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="137" t="inlineStr">
+      <c r="A16" s="257" t="inlineStr">
         <is>
           <t>ALM-0004</t>
         </is>
       </c>
-      <c r="B16" s="138" t="inlineStr">
+      <c r="B16" s="258" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C16" s="138" t="inlineStr">
+      <c r="C16" s="258" t="inlineStr">
         <is>
           <t>13:51:49</t>
         </is>
       </c>
-      <c r="D16" s="139" t="inlineStr">
+      <c r="D16" s="259" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E16" s="139" t="inlineStr">
+      <c r="E16" s="259" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F16" s="139" t="inlineStr">
+      <c r="F16" s="259" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -2216,33 +2602,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H16" s="138" t="inlineStr">
+      <c r="H16" s="258" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I16" s="138" t="n">
+      <c r="I16" s="258" t="n">
         <v>1</v>
       </c>
-      <c r="J16" s="139" t="inlineStr">
+      <c r="J16" s="259" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K16" s="138" t="n">
+      <c r="K16" s="258" t="n">
         <v>62.9</v>
       </c>
-      <c r="L16" s="155" t="inlineStr">
+      <c r="L16" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M16" s="141" t="inlineStr">
+      <c r="M16" s="261" t="inlineStr">
         <is>
           <t>ALARM RAISED</t>
         </is>
       </c>
-      <c r="N16" s="138" t="n">
+      <c r="N16" s="258" t="n">
         <v>0</v>
       </c>
       <c r="O16" s="6" t="inlineStr">
@@ -2250,7 +2636,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P16" s="139" t="inlineStr">
+      <c r="P16" s="259" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -2262,32 +2648,32 @@
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="147" t="inlineStr">
+      <c r="A17" s="277" t="inlineStr">
         <is>
           <t>ALM-0004</t>
         </is>
       </c>
-      <c r="B17" s="148" t="inlineStr">
+      <c r="B17" s="278" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C17" s="148" t="inlineStr">
+      <c r="C17" s="278" t="inlineStr">
         <is>
           <t>13:51:50</t>
         </is>
       </c>
-      <c r="D17" s="149" t="inlineStr">
+      <c r="D17" s="279" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E17" s="149" t="inlineStr">
+      <c r="E17" s="279" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F17" s="149" t="inlineStr">
+      <c r="F17" s="279" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -2297,33 +2683,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H17" s="148" t="inlineStr">
+      <c r="H17" s="278" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I17" s="148" t="n">
+      <c r="I17" s="278" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="149" t="inlineStr">
+      <c r="J17" s="279" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K17" s="148" t="n">
+      <c r="K17" s="278" t="n">
         <v>60.7</v>
       </c>
-      <c r="L17" s="155" t="inlineStr">
+      <c r="L17" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M17" s="151" t="inlineStr">
+      <c r="M17" s="281" t="inlineStr">
         <is>
           <t>ALARM ACTIVE</t>
         </is>
       </c>
-      <c r="N17" s="148" t="n">
+      <c r="N17" s="278" t="n">
         <v>0.3</v>
       </c>
       <c r="O17" s="18" t="inlineStr">
@@ -2331,7 +2717,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P17" s="149" t="inlineStr">
+      <c r="P17" s="279" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -2343,32 +2729,32 @@
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="152" t="inlineStr">
+      <c r="A18" s="272" t="inlineStr">
         <is>
           <t>ALM-0004</t>
         </is>
       </c>
-      <c r="B18" s="153" t="inlineStr">
+      <c r="B18" s="273" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C18" s="153" t="inlineStr">
+      <c r="C18" s="273" t="inlineStr">
         <is>
           <t>13:52:00</t>
         </is>
       </c>
-      <c r="D18" s="154" t="inlineStr">
+      <c r="D18" s="274" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E18" s="154" t="inlineStr">
+      <c r="E18" s="274" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F18" s="154" t="inlineStr">
+      <c r="F18" s="274" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -2378,33 +2764,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H18" s="153" t="inlineStr">
+      <c r="H18" s="273" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I18" s="153" t="n">
+      <c r="I18" s="273" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="154" t="inlineStr">
+      <c r="J18" s="274" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K18" s="153" t="n">
+      <c r="K18" s="273" t="n">
         <v>72.90000000000001</v>
       </c>
-      <c r="L18" s="155" t="inlineStr">
+      <c r="L18" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M18" s="156" t="inlineStr">
+      <c r="M18" s="276" t="inlineStr">
         <is>
           <t>ALARM ACTIVE</t>
         </is>
       </c>
-      <c r="N18" s="153" t="n">
+      <c r="N18" s="273" t="n">
         <v>10.4</v>
       </c>
       <c r="O18" s="12" t="inlineStr">
@@ -2412,7 +2798,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P18" s="154" t="inlineStr">
+      <c r="P18" s="274" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -2424,32 +2810,32 @@
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="147" t="inlineStr">
+      <c r="A19" s="277" t="inlineStr">
         <is>
           <t>ALM-0004</t>
         </is>
       </c>
-      <c r="B19" s="148" t="inlineStr">
+      <c r="B19" s="278" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C19" s="148" t="inlineStr">
+      <c r="C19" s="278" t="inlineStr">
         <is>
           <t>13:52:10</t>
         </is>
       </c>
-      <c r="D19" s="149" t="inlineStr">
+      <c r="D19" s="279" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E19" s="149" t="inlineStr">
+      <c r="E19" s="279" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F19" s="149" t="inlineStr">
+      <c r="F19" s="279" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -2459,33 +2845,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H19" s="148" t="inlineStr">
+      <c r="H19" s="278" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I19" s="148" t="n">
+      <c r="I19" s="278" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="149" t="inlineStr">
+      <c r="J19" s="279" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K19" s="148" t="n">
+      <c r="K19" s="278" t="n">
         <v>91.8</v>
       </c>
-      <c r="L19" s="155" t="inlineStr">
+      <c r="L19" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M19" s="151" t="inlineStr">
+      <c r="M19" s="281" t="inlineStr">
         <is>
           <t>ALARM ACTIVE</t>
         </is>
       </c>
-      <c r="N19" s="148" t="n">
+      <c r="N19" s="278" t="n">
         <v>20.5</v>
       </c>
       <c r="O19" s="18" t="inlineStr">
@@ -2493,7 +2879,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P19" s="149" t="inlineStr">
+      <c r="P19" s="279" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -2505,32 +2891,32 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="152" t="inlineStr">
+      <c r="A20" s="272" t="inlineStr">
         <is>
           <t>ALM-0004</t>
         </is>
       </c>
-      <c r="B20" s="153" t="inlineStr">
+      <c r="B20" s="273" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C20" s="153" t="inlineStr">
+      <c r="C20" s="273" t="inlineStr">
         <is>
           <t>13:52:20</t>
         </is>
       </c>
-      <c r="D20" s="154" t="inlineStr">
+      <c r="D20" s="274" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E20" s="154" t="inlineStr">
+      <c r="E20" s="274" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F20" s="154" t="inlineStr">
+      <c r="F20" s="274" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -2540,33 +2926,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H20" s="153" t="inlineStr">
+      <c r="H20" s="273" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I20" s="153" t="n">
+      <c r="I20" s="273" t="n">
         <v>1</v>
       </c>
-      <c r="J20" s="154" t="inlineStr">
+      <c r="J20" s="274" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K20" s="153" t="n">
+      <c r="K20" s="273" t="n">
         <v>89</v>
       </c>
-      <c r="L20" s="155" t="inlineStr">
+      <c r="L20" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M20" s="156" t="inlineStr">
+      <c r="M20" s="276" t="inlineStr">
         <is>
           <t>ALARM ACTIVE</t>
         </is>
       </c>
-      <c r="N20" s="153" t="n">
+      <c r="N20" s="273" t="n">
         <v>30.7</v>
       </c>
       <c r="O20" s="12" t="inlineStr">
@@ -2574,7 +2960,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P20" s="154" t="inlineStr">
+      <c r="P20" s="274" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -2586,32 +2972,32 @@
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="147" t="inlineStr">
+      <c r="A21" s="277" t="inlineStr">
         <is>
           <t>ALM-0004</t>
         </is>
       </c>
-      <c r="B21" s="148" t="inlineStr">
+      <c r="B21" s="278" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C21" s="148" t="inlineStr">
+      <c r="C21" s="278" t="inlineStr">
         <is>
           <t>13:52:21</t>
         </is>
       </c>
-      <c r="D21" s="149" t="inlineStr">
+      <c r="D21" s="279" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E21" s="149" t="inlineStr">
+      <c r="E21" s="279" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F21" s="149" t="inlineStr">
+      <c r="F21" s="279" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -2621,33 +3007,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H21" s="148" t="inlineStr">
+      <c r="H21" s="278" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I21" s="148" t="n">
+      <c r="I21" s="278" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="149" t="inlineStr">
+      <c r="J21" s="279" t="inlineStr">
         <is>
           <t>CLEAR</t>
         </is>
       </c>
-      <c r="K21" s="148" t="n">
+      <c r="K21" s="278" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="155" t="inlineStr">
+      <c r="L21" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M21" s="101" t="inlineStr">
+      <c r="M21" s="221" t="inlineStr">
         <is>
           <t>SESSION ENDED</t>
         </is>
       </c>
-      <c r="N21" s="148" t="n">
+      <c r="N21" s="278" t="n">
         <v>32.1</v>
       </c>
       <c r="O21" s="18" t="inlineStr">
@@ -2655,7 +3041,7 @@
           <t>NO ACTION REQUIRED</t>
         </is>
       </c>
-      <c r="P21" s="149" t="inlineStr">
+      <c r="P21" s="279" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -2667,32 +3053,32 @@
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="137" t="inlineStr">
+      <c r="A22" s="257" t="inlineStr">
         <is>
           <t>ALM-0001</t>
         </is>
       </c>
-      <c r="B22" s="138" t="inlineStr">
+      <c r="B22" s="258" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C22" s="138" t="inlineStr">
+      <c r="C22" s="258" t="inlineStr">
         <is>
           <t>14:21:48</t>
         </is>
       </c>
-      <c r="D22" s="139" t="inlineStr">
+      <c r="D22" s="259" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E22" s="139" t="inlineStr">
+      <c r="E22" s="259" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F22" s="139" t="inlineStr">
+      <c r="F22" s="259" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -2702,33 +3088,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H22" s="138" t="inlineStr">
+      <c r="H22" s="258" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I22" s="138" t="n">
+      <c r="I22" s="258" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="139" t="inlineStr">
+      <c r="J22" s="259" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K22" s="138" t="n">
+      <c r="K22" s="258" t="n">
         <v>94.8</v>
       </c>
-      <c r="L22" s="155" t="inlineStr">
+      <c r="L22" s="265" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M22" s="141" t="inlineStr">
+      <c r="M22" s="261" t="inlineStr">
         <is>
           <t>ALARM RAISED</t>
         </is>
       </c>
-      <c r="N22" s="138" t="n">
+      <c r="N22" s="258" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="6" t="inlineStr">
@@ -2736,7 +3122,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P22" s="139" t="inlineStr">
+      <c r="P22" s="259" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -2748,32 +3134,32 @@
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="147" t="inlineStr">
+      <c r="A23" s="277" t="inlineStr">
         <is>
           <t>ALM-0001</t>
         </is>
       </c>
-      <c r="B23" s="148" t="inlineStr">
+      <c r="B23" s="278" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C23" s="148" t="inlineStr">
+      <c r="C23" s="278" t="inlineStr">
         <is>
           <t>14:21:49</t>
         </is>
       </c>
-      <c r="D23" s="149" t="inlineStr">
+      <c r="D23" s="279" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E23" s="149" t="inlineStr">
+      <c r="E23" s="279" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F23" s="149" t="inlineStr">
+      <c r="F23" s="279" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -2783,33 +3169,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H23" s="148" t="inlineStr">
+      <c r="H23" s="278" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I23" s="148" t="n">
+      <c r="I23" s="278" t="n">
         <v>1</v>
       </c>
-      <c r="J23" s="149" t="inlineStr">
+      <c r="J23" s="279" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K23" s="148" t="n">
+      <c r="K23" s="278" t="n">
         <v>94.59999999999999</v>
       </c>
-      <c r="L23" s="155" t="inlineStr">
+      <c r="L23" s="265" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M23" s="151" t="inlineStr">
+      <c r="M23" s="281" t="inlineStr">
         <is>
           <t>ALARM ACTIVE</t>
         </is>
       </c>
-      <c r="N23" s="148" t="n">
+      <c r="N23" s="278" t="n">
         <v>0.2</v>
       </c>
       <c r="O23" s="18" t="inlineStr">
@@ -2817,7 +3203,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P23" s="149" t="inlineStr">
+      <c r="P23" s="279" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -2829,32 +3215,32 @@
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="152" t="inlineStr">
+      <c r="A24" s="272" t="inlineStr">
         <is>
           <t>ALM-0001</t>
         </is>
       </c>
-      <c r="B24" s="153" t="inlineStr">
+      <c r="B24" s="273" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C24" s="153" t="inlineStr">
+      <c r="C24" s="273" t="inlineStr">
         <is>
           <t>14:21:59</t>
         </is>
       </c>
-      <c r="D24" s="154" t="inlineStr">
+      <c r="D24" s="274" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E24" s="154" t="inlineStr">
+      <c r="E24" s="274" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F24" s="154" t="inlineStr">
+      <c r="F24" s="274" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -2864,33 +3250,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H24" s="153" t="inlineStr">
+      <c r="H24" s="273" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I24" s="153" t="n">
+      <c r="I24" s="273" t="n">
         <v>1</v>
       </c>
-      <c r="J24" s="154" t="inlineStr">
+      <c r="J24" s="274" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K24" s="153" t="n">
+      <c r="K24" s="273" t="n">
         <v>93.3</v>
       </c>
-      <c r="L24" s="155" t="inlineStr">
+      <c r="L24" s="265" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M24" s="156" t="inlineStr">
+      <c r="M24" s="276" t="inlineStr">
         <is>
           <t>ALARM ACTIVE</t>
         </is>
       </c>
-      <c r="N24" s="153" t="n">
+      <c r="N24" s="273" t="n">
         <v>10.3</v>
       </c>
       <c r="O24" s="12" t="inlineStr">
@@ -2898,7 +3284,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P24" s="154" t="inlineStr">
+      <c r="P24" s="274" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -2910,32 +3296,32 @@
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="117" t="inlineStr">
+      <c r="A25" s="252" t="inlineStr">
         <is>
           <t>ALM-0001</t>
         </is>
       </c>
-      <c r="B25" s="118" t="inlineStr">
+      <c r="B25" s="253" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C25" s="118" t="inlineStr">
+      <c r="C25" s="253" t="inlineStr">
         <is>
           <t>14:22:06</t>
         </is>
       </c>
-      <c r="D25" s="119" t="inlineStr">
+      <c r="D25" s="254" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E25" s="119" t="inlineStr">
+      <c r="E25" s="254" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F25" s="119" t="inlineStr">
+      <c r="F25" s="254" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -2945,33 +3331,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H25" s="118" t="inlineStr">
+      <c r="H25" s="253" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I25" s="118" t="n">
+      <c r="I25" s="253" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="119" t="inlineStr">
+      <c r="J25" s="254" t="inlineStr">
         <is>
           <t>CLEAR</t>
         </is>
       </c>
-      <c r="K25" s="118" t="n">
+      <c r="K25" s="253" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="155" t="inlineStr">
+      <c r="L25" s="265" t="inlineStr">
         <is>
           <t>CLEAR</t>
         </is>
       </c>
-      <c r="M25" s="121" t="inlineStr">
+      <c r="M25" s="256" t="inlineStr">
         <is>
           <t>ALARM CLEARED</t>
         </is>
       </c>
-      <c r="N25" s="118" t="n">
+      <c r="N25" s="253" t="n">
         <v>18</v>
       </c>
       <c r="O25" s="34" t="inlineStr">
@@ -2979,7 +3365,7 @@
           <t>NO ACTION REQUIRED</t>
         </is>
       </c>
-      <c r="P25" s="119" t="inlineStr">
+      <c r="P25" s="254" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -2991,32 +3377,32 @@
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="137" t="inlineStr">
+      <c r="A26" s="257" t="inlineStr">
         <is>
           <t>ALM-0002</t>
         </is>
       </c>
-      <c r="B26" s="138" t="inlineStr">
+      <c r="B26" s="258" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C26" s="138" t="inlineStr">
+      <c r="C26" s="258" t="inlineStr">
         <is>
           <t>14:22:10</t>
         </is>
       </c>
-      <c r="D26" s="139" t="inlineStr">
+      <c r="D26" s="259" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E26" s="139" t="inlineStr">
+      <c r="E26" s="259" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F26" s="139" t="inlineStr">
+      <c r="F26" s="259" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -3026,33 +3412,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H26" s="138" t="inlineStr">
+      <c r="H26" s="258" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I26" s="138" t="n">
+      <c r="I26" s="258" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="139" t="inlineStr">
+      <c r="J26" s="259" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K26" s="138" t="n">
+      <c r="K26" s="258" t="n">
         <v>93.5</v>
       </c>
-      <c r="L26" s="155" t="inlineStr">
+      <c r="L26" s="265" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M26" s="141" t="inlineStr">
+      <c r="M26" s="261" t="inlineStr">
         <is>
           <t>ALARM RAISED</t>
         </is>
       </c>
-      <c r="N26" s="138" t="n">
+      <c r="N26" s="258" t="n">
         <v>0</v>
       </c>
       <c r="O26" s="6" t="inlineStr">
@@ -3060,7 +3446,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P26" s="139" t="inlineStr">
+      <c r="P26" s="259" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -3072,32 +3458,32 @@
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="147" t="inlineStr">
+      <c r="A27" s="277" t="inlineStr">
         <is>
           <t>ALM-0002</t>
         </is>
       </c>
-      <c r="B27" s="148" t="inlineStr">
+      <c r="B27" s="278" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C27" s="148" t="inlineStr">
+      <c r="C27" s="278" t="inlineStr">
         <is>
           <t>14:22:11</t>
         </is>
       </c>
-      <c r="D27" s="149" t="inlineStr">
+      <c r="D27" s="279" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E27" s="149" t="inlineStr">
+      <c r="E27" s="279" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F27" s="149" t="inlineStr">
+      <c r="F27" s="279" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -3107,33 +3493,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H27" s="148" t="inlineStr">
+      <c r="H27" s="278" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I27" s="148" t="n">
+      <c r="I27" s="278" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="149" t="inlineStr">
+      <c r="J27" s="279" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K27" s="148" t="n">
+      <c r="K27" s="278" t="n">
         <v>93.7</v>
       </c>
-      <c r="L27" s="155" t="inlineStr">
+      <c r="L27" s="265" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M27" s="151" t="inlineStr">
+      <c r="M27" s="281" t="inlineStr">
         <is>
           <t>ALARM ACTIVE</t>
         </is>
       </c>
-      <c r="N27" s="148" t="n">
+      <c r="N27" s="278" t="n">
         <v>0.3</v>
       </c>
       <c r="O27" s="18" t="inlineStr">
@@ -3141,7 +3527,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P27" s="149" t="inlineStr">
+      <c r="P27" s="279" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -3153,32 +3539,32 @@
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="152" t="inlineStr">
+      <c r="A28" s="272" t="inlineStr">
         <is>
           <t>ALM-0002</t>
         </is>
       </c>
-      <c r="B28" s="153" t="inlineStr">
+      <c r="B28" s="273" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C28" s="153" t="inlineStr">
+      <c r="C28" s="273" t="inlineStr">
         <is>
           <t>14:22:14</t>
         </is>
       </c>
-      <c r="D28" s="154" t="inlineStr">
+      <c r="D28" s="274" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E28" s="154" t="inlineStr">
+      <c r="E28" s="274" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F28" s="154" t="inlineStr">
+      <c r="F28" s="274" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -3188,23 +3574,23 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H28" s="153" t="inlineStr">
+      <c r="H28" s="273" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I28" s="153" t="n">
+      <c r="I28" s="273" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="154" t="inlineStr">
+      <c r="J28" s="274" t="inlineStr">
         <is>
           <t>CLEAR</t>
         </is>
       </c>
-      <c r="K28" s="153" t="n">
+      <c r="K28" s="273" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="155" t="inlineStr">
+      <c r="L28" s="265" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -3214,7 +3600,7 @@
           <t>SESSION ENDED</t>
         </is>
       </c>
-      <c r="N28" s="153" t="n">
+      <c r="N28" s="273" t="n">
         <v>4.4</v>
       </c>
       <c r="O28" s="12" t="inlineStr">
@@ -3222,7 +3608,7 @@
           <t>NO ACTION REQUIRED</t>
         </is>
       </c>
-      <c r="P28" s="154" t="inlineStr">
+      <c r="P28" s="274" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -3234,32 +3620,32 @@
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="137" t="inlineStr">
+      <c r="A29" s="257" t="inlineStr">
         <is>
           <t>ALM-0001</t>
         </is>
       </c>
-      <c r="B29" s="138" t="inlineStr">
+      <c r="B29" s="258" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C29" s="138" t="inlineStr">
+      <c r="C29" s="258" t="inlineStr">
         <is>
           <t>15:45:05</t>
         </is>
       </c>
-      <c r="D29" s="139" t="inlineStr">
+      <c r="D29" s="259" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E29" s="139" t="inlineStr">
+      <c r="E29" s="259" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F29" s="139" t="inlineStr">
+      <c r="F29" s="259" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -3269,33 +3655,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H29" s="138" t="inlineStr">
+      <c r="H29" s="258" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I29" s="138" t="n">
+      <c r="I29" s="258" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="139" t="inlineStr">
+      <c r="J29" s="259" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K29" s="138" t="n">
+      <c r="K29" s="258" t="n">
         <v>88.5</v>
       </c>
-      <c r="L29" s="155" t="inlineStr">
+      <c r="L29" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M29" s="141" t="inlineStr">
+      <c r="M29" s="261" t="inlineStr">
         <is>
           <t>ALARM RAISED</t>
         </is>
       </c>
-      <c r="N29" s="138" t="n">
+      <c r="N29" s="258" t="n">
         <v>0</v>
       </c>
       <c r="O29" s="6" t="inlineStr">
@@ -3303,7 +3689,7 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P29" s="139" t="inlineStr">
+      <c r="P29" s="259" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
@@ -3313,39 +3699,39 @@
           <t>snapshots\ALM-0001_20260609_154505.jpg</t>
         </is>
       </c>
-      <c r="R29" s="139" t="inlineStr">
+      <c r="R29" s="259" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER — alarm triggered</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="152" t="inlineStr">
+      <c r="A30" s="272" t="inlineStr">
         <is>
           <t>ALM-0001</t>
         </is>
       </c>
-      <c r="B30" s="153" t="inlineStr">
+      <c r="B30" s="273" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C30" s="153" t="inlineStr">
+      <c r="C30" s="273" t="inlineStr">
         <is>
           <t>15:45:05</t>
         </is>
       </c>
-      <c r="D30" s="154" t="inlineStr">
+      <c r="D30" s="274" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E30" s="154" t="inlineStr">
+      <c r="E30" s="274" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F30" s="154" t="inlineStr">
+      <c r="F30" s="274" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -3355,33 +3741,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H30" s="153" t="inlineStr">
+      <c r="H30" s="273" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I30" s="153" t="n">
+      <c r="I30" s="273" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="154" t="inlineStr">
+      <c r="J30" s="274" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K30" s="153" t="n">
+      <c r="K30" s="273" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="L30" s="155" t="inlineStr">
+      <c r="L30" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M30" s="156" t="inlineStr">
+      <c r="M30" s="276" t="inlineStr">
         <is>
           <t>ALARM ACTIVE</t>
         </is>
       </c>
-      <c r="N30" s="153" t="n">
+      <c r="N30" s="273" t="n">
         <v>0.2</v>
       </c>
       <c r="O30" s="12" t="inlineStr">
@@ -3389,45 +3775,45 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P30" s="154" t="inlineStr">
+      <c r="P30" s="274" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
       </c>
       <c r="Q30" s="12" t="inlineStr"/>
-      <c r="R30" s="154" t="inlineStr">
+      <c r="R30" s="274" t="inlineStr">
         <is>
           <t>Ongoing — 0s elapsed</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="147" t="inlineStr">
+      <c r="A31" s="277" t="inlineStr">
         <is>
           <t>ALM-0001</t>
         </is>
       </c>
-      <c r="B31" s="148" t="inlineStr">
+      <c r="B31" s="278" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C31" s="148" t="inlineStr">
+      <c r="C31" s="278" t="inlineStr">
         <is>
           <t>15:45:15</t>
         </is>
       </c>
-      <c r="D31" s="149" t="inlineStr">
+      <c r="D31" s="279" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E31" s="149" t="inlineStr">
+      <c r="E31" s="279" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F31" s="149" t="inlineStr">
+      <c r="F31" s="279" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -3437,33 +3823,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H31" s="148" t="inlineStr">
+      <c r="H31" s="278" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I31" s="148" t="n">
+      <c r="I31" s="278" t="n">
         <v>1</v>
       </c>
-      <c r="J31" s="149" t="inlineStr">
+      <c r="J31" s="279" t="inlineStr">
         <is>
           <t>SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="K31" s="148" t="n">
+      <c r="K31" s="278" t="n">
         <v>93.09999999999999</v>
       </c>
-      <c r="L31" s="155" t="inlineStr">
+      <c r="L31" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M31" s="151" t="inlineStr">
+      <c r="M31" s="281" t="inlineStr">
         <is>
           <t>ALARM ACTIVE</t>
         </is>
       </c>
-      <c r="N31" s="148" t="n">
+      <c r="N31" s="278" t="n">
         <v>10.4</v>
       </c>
       <c r="O31" s="18" t="inlineStr">
@@ -3471,45 +3857,45 @@
           <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
         </is>
       </c>
-      <c r="P31" s="149" t="inlineStr">
+      <c r="P31" s="279" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
       </c>
       <c r="Q31" s="18" t="inlineStr"/>
-      <c r="R31" s="149" t="inlineStr">
+      <c r="R31" s="279" t="inlineStr">
         <is>
           <t>Ongoing — 10s elapsed</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="152" t="inlineStr">
+      <c r="A32" s="272" t="inlineStr">
         <is>
           <t>ALM-0001</t>
         </is>
       </c>
-      <c r="B32" s="153" t="inlineStr">
+      <c r="B32" s="273" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C32" s="153" t="inlineStr">
+      <c r="C32" s="273" t="inlineStr">
         <is>
           <t>15:45:25</t>
         </is>
       </c>
-      <c r="D32" s="154" t="inlineStr">
+      <c r="D32" s="274" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E32" s="154" t="inlineStr">
+      <c r="E32" s="274" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F32" s="154" t="inlineStr">
+      <c r="F32" s="274" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -3519,33 +3905,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H32" s="153" t="inlineStr">
+      <c r="H32" s="273" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I32" s="153" t="n">
+      <c r="I32" s="273" t="n">
         <v>2</v>
       </c>
-      <c r="J32" s="154" t="inlineStr">
+      <c r="J32" s="274" t="inlineStr">
         <is>
           <t>COORDINATED INTRUSION</t>
         </is>
       </c>
-      <c r="K32" s="153" t="n">
+      <c r="K32" s="273" t="n">
         <v>91.2</v>
       </c>
-      <c r="L32" s="155" t="inlineStr">
+      <c r="L32" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M32" s="156" t="inlineStr">
+      <c r="M32" s="276" t="inlineStr">
         <is>
           <t>ALARM ACTIVE</t>
         </is>
       </c>
-      <c r="N32" s="153" t="n">
+      <c r="N32" s="273" t="n">
         <v>20.6</v>
       </c>
       <c r="O32" s="12" t="inlineStr">
@@ -3553,45 +3939,45 @@
           <t>DISPATCH SECURITY — COORDINATED ENTRY</t>
         </is>
       </c>
-      <c r="P32" s="154" t="inlineStr">
+      <c r="P32" s="274" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
       </c>
       <c r="Q32" s="12" t="inlineStr"/>
-      <c r="R32" s="154" t="inlineStr">
+      <c r="R32" s="274" t="inlineStr">
         <is>
           <t>Ongoing — 21s elapsed</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="157" t="inlineStr">
+      <c r="A33" s="277" t="inlineStr">
         <is>
           <t>ALM-0001</t>
         </is>
       </c>
-      <c r="B33" s="158" t="inlineStr">
+      <c r="B33" s="278" t="inlineStr">
         <is>
           <t>09-06-2026</t>
         </is>
       </c>
-      <c r="C33" s="158" t="inlineStr">
+      <c r="C33" s="278" t="inlineStr">
         <is>
           <t>15:45:33</t>
         </is>
       </c>
-      <c r="D33" s="159" t="inlineStr">
+      <c r="D33" s="279" t="inlineStr">
         <is>
           <t>AIRTEL-ASM-BTS-001</t>
         </is>
       </c>
-      <c r="E33" s="159" t="inlineStr">
+      <c r="E33" s="279" t="inlineStr">
         <is>
           <t>Guwahati North BTS</t>
         </is>
       </c>
-      <c r="F33" s="159" t="inlineStr">
+      <c r="F33" s="279" t="inlineStr">
         <is>
           <t>Guwahati, Assam</t>
         </is>
@@ -3601,33 +3987,33 @@
           <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
         </is>
       </c>
-      <c r="H33" s="158" t="inlineStr">
+      <c r="H33" s="278" t="inlineStr">
         <is>
           <t>CAM-BTS-01</t>
         </is>
       </c>
-      <c r="I33" s="158" t="n">
+      <c r="I33" s="278" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="159" t="inlineStr">
+      <c r="J33" s="279" t="inlineStr">
         <is>
           <t>CLEAR</t>
         </is>
       </c>
-      <c r="K33" s="158" t="n">
+      <c r="K33" s="278" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="160" t="inlineStr">
+      <c r="L33" s="265" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M33" s="161" t="inlineStr">
+      <c r="M33" s="221" t="inlineStr">
         <is>
           <t>SESSION ENDED</t>
         </is>
       </c>
-      <c r="N33" s="158" t="n">
+      <c r="N33" s="278" t="n">
         <v>28.5</v>
       </c>
       <c r="O33" s="18" t="inlineStr">
@@ -3635,13 +4021,2059 @@
           <t>NO ACTION REQUIRED</t>
         </is>
       </c>
-      <c r="P33" s="159" t="inlineStr">
+      <c r="P33" s="279" t="inlineStr">
         <is>
           <t>NOC-OPS-ASM-01</t>
         </is>
       </c>
       <c r="Q33" s="18" t="inlineStr"/>
-      <c r="R33" s="159" t="inlineStr">
+      <c r="R33" s="279" t="inlineStr">
+        <is>
+          <t>Session ended by operator</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="257" t="inlineStr">
+        <is>
+          <t>ALM-0001</t>
+        </is>
+      </c>
+      <c r="B34" s="258" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C34" s="258" t="inlineStr">
+        <is>
+          <t>11:32:22</t>
+        </is>
+      </c>
+      <c r="D34" s="259" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E34" s="259" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F34" s="259" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H34" s="258" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I34" s="258" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" s="259" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION</t>
+        </is>
+      </c>
+      <c r="K34" s="258" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="L34" s="265" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M34" s="261" t="inlineStr">
+        <is>
+          <t>ALARM RAISED</t>
+        </is>
+      </c>
+      <c r="N34" s="258" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>DISPATCH SECURITY — COORDINATED ENTRY</t>
+        </is>
+      </c>
+      <c r="P34" s="259" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION — alarm triggered</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="277" t="inlineStr">
+        <is>
+          <t>ALM-0001</t>
+        </is>
+      </c>
+      <c r="B35" s="278" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C35" s="278" t="inlineStr">
+        <is>
+          <t>11:32:23</t>
+        </is>
+      </c>
+      <c r="D35" s="279" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E35" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F35" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G35" s="18" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H35" s="278" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I35" s="278" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" s="279" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION</t>
+        </is>
+      </c>
+      <c r="K35" s="278" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="L35" s="265" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M35" s="281" t="inlineStr">
+        <is>
+          <t>ALARM ACTIVE</t>
+        </is>
+      </c>
+      <c r="N35" s="278" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O35" s="18" t="inlineStr">
+        <is>
+          <t>DISPATCH SECURITY — COORDINATED ENTRY</t>
+        </is>
+      </c>
+      <c r="P35" s="279" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q35" s="18" t="inlineStr">
+        <is>
+          <t>Ongoing — 1s elapsed</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="272" t="inlineStr">
+        <is>
+          <t>ALM-0001</t>
+        </is>
+      </c>
+      <c r="B36" s="273" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C36" s="273" t="inlineStr">
+        <is>
+          <t>11:32:33</t>
+        </is>
+      </c>
+      <c r="D36" s="274" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E36" s="274" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F36" s="274" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H36" s="273" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I36" s="273" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" s="274" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION</t>
+        </is>
+      </c>
+      <c r="K36" s="273" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="L36" s="265" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M36" s="276" t="inlineStr">
+        <is>
+          <t>ALARM ACTIVE</t>
+        </is>
+      </c>
+      <c r="N36" s="273" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="O36" s="12" t="inlineStr">
+        <is>
+          <t>DISPATCH SECURITY — COORDINATED ENTRY</t>
+        </is>
+      </c>
+      <c r="P36" s="274" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q36" s="12" t="inlineStr">
+        <is>
+          <t>Ongoing — 11s elapsed</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="277" t="inlineStr">
+        <is>
+          <t>ALM-0001</t>
+        </is>
+      </c>
+      <c r="B37" s="278" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C37" s="278" t="inlineStr">
+        <is>
+          <t>11:32:43</t>
+        </is>
+      </c>
+      <c r="D37" s="279" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E37" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F37" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G37" s="18" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H37" s="278" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I37" s="278" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" s="279" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION</t>
+        </is>
+      </c>
+      <c r="K37" s="278" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="L37" s="265" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M37" s="281" t="inlineStr">
+        <is>
+          <t>ALARM ACTIVE</t>
+        </is>
+      </c>
+      <c r="N37" s="278" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>DISPATCH SECURITY — COORDINATED ENTRY</t>
+        </is>
+      </c>
+      <c r="P37" s="279" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q37" s="18" t="inlineStr">
+        <is>
+          <t>Ongoing — 21s elapsed</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="252" t="inlineStr">
+        <is>
+          <t>ALM-0001</t>
+        </is>
+      </c>
+      <c r="B38" s="253" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C38" s="253" t="inlineStr">
+        <is>
+          <t>11:32:46</t>
+        </is>
+      </c>
+      <c r="D38" s="254" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E38" s="254" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F38" s="254" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G38" s="34" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H38" s="253" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I38" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="254" t="inlineStr">
+        <is>
+          <t>CLEAR</t>
+        </is>
+      </c>
+      <c r="K38" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="265" t="inlineStr">
+        <is>
+          <t>CLEAR</t>
+        </is>
+      </c>
+      <c r="M38" s="256" t="inlineStr">
+        <is>
+          <t>ALARM CLEARED</t>
+        </is>
+      </c>
+      <c r="N38" s="253" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="O38" s="34" t="inlineStr">
+        <is>
+          <t>NO ACTION REQUIRED</t>
+        </is>
+      </c>
+      <c r="P38" s="254" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q38" s="34" t="inlineStr">
+        <is>
+          <t>Area clear after 23.7s</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="257" t="inlineStr">
+        <is>
+          <t>ALM-0002</t>
+        </is>
+      </c>
+      <c r="B39" s="258" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C39" s="258" t="inlineStr">
+        <is>
+          <t>11:32:49</t>
+        </is>
+      </c>
+      <c r="D39" s="259" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E39" s="259" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F39" s="259" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H39" s="258" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I39" s="258" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" s="259" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION</t>
+        </is>
+      </c>
+      <c r="K39" s="258" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="L39" s="265" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M39" s="261" t="inlineStr">
+        <is>
+          <t>ALARM RAISED</t>
+        </is>
+      </c>
+      <c r="N39" s="258" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="6" t="inlineStr">
+        <is>
+          <t>DISPATCH SECURITY — COORDINATED ENTRY</t>
+        </is>
+      </c>
+      <c r="P39" s="259" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION — alarm triggered</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="272" t="inlineStr">
+        <is>
+          <t>ALM-0002</t>
+        </is>
+      </c>
+      <c r="B40" s="273" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C40" s="273" t="inlineStr">
+        <is>
+          <t>11:32:49</t>
+        </is>
+      </c>
+      <c r="D40" s="274" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E40" s="274" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F40" s="274" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H40" s="273" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I40" s="273" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" s="274" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION</t>
+        </is>
+      </c>
+      <c r="K40" s="273" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="L40" s="265" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M40" s="276" t="inlineStr">
+        <is>
+          <t>ALARM ACTIVE</t>
+        </is>
+      </c>
+      <c r="N40" s="273" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O40" s="12" t="inlineStr">
+        <is>
+          <t>DISPATCH SECURITY — COORDINATED ENTRY</t>
+        </is>
+      </c>
+      <c r="P40" s="274" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q40" s="12" t="inlineStr">
+        <is>
+          <t>Ongoing — 0s elapsed</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="277" t="inlineStr">
+        <is>
+          <t>ALM-0002</t>
+        </is>
+      </c>
+      <c r="B41" s="278" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C41" s="278" t="inlineStr">
+        <is>
+          <t>11:32:59</t>
+        </is>
+      </c>
+      <c r="D41" s="279" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E41" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F41" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G41" s="18" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H41" s="278" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I41" s="278" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="279" t="inlineStr">
+        <is>
+          <t>SINGLE INTRUDER</t>
+        </is>
+      </c>
+      <c r="K41" s="278" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="L41" s="265" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M41" s="281" t="inlineStr">
+        <is>
+          <t>ALARM ACTIVE</t>
+        </is>
+      </c>
+      <c r="N41" s="278" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O41" s="18" t="inlineStr">
+        <is>
+          <t>DISPATCH SECURITY — SINGLE INTRUDER</t>
+        </is>
+      </c>
+      <c r="P41" s="279" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q41" s="18" t="inlineStr">
+        <is>
+          <t>Ongoing — 11s elapsed</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="272" t="inlineStr">
+        <is>
+          <t>ALM-0002</t>
+        </is>
+      </c>
+      <c r="B42" s="273" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C42" s="273" t="inlineStr">
+        <is>
+          <t>11:33:10</t>
+        </is>
+      </c>
+      <c r="D42" s="274" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E42" s="274" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F42" s="274" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H42" s="273" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I42" s="273" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" s="274" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION</t>
+        </is>
+      </c>
+      <c r="K42" s="273" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="L42" s="265" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M42" s="276" t="inlineStr">
+        <is>
+          <t>ALARM ACTIVE</t>
+        </is>
+      </c>
+      <c r="N42" s="273" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="O42" s="12" t="inlineStr">
+        <is>
+          <t>DISPATCH SECURITY — COORDINATED ENTRY</t>
+        </is>
+      </c>
+      <c r="P42" s="274" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q42" s="12" t="inlineStr">
+        <is>
+          <t>Ongoing — 21s elapsed</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="277" t="inlineStr">
+        <is>
+          <t>ALM-0002</t>
+        </is>
+      </c>
+      <c r="B43" s="278" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C43" s="278" t="inlineStr">
+        <is>
+          <t>11:33:20</t>
+        </is>
+      </c>
+      <c r="D43" s="279" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E43" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F43" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G43" s="18" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H43" s="278" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I43" s="278" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" s="279" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION</t>
+        </is>
+      </c>
+      <c r="K43" s="278" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="L43" s="265" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M43" s="281" t="inlineStr">
+        <is>
+          <t>ALARM ACTIVE</t>
+        </is>
+      </c>
+      <c r="N43" s="278" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="O43" s="18" t="inlineStr">
+        <is>
+          <t>DISPATCH SECURITY — COORDINATED ENTRY</t>
+        </is>
+      </c>
+      <c r="P43" s="279" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q43" s="18" t="inlineStr">
+        <is>
+          <t>Ongoing — 31s elapsed</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="272" t="inlineStr">
+        <is>
+          <t>ALM-0002</t>
+        </is>
+      </c>
+      <c r="B44" s="273" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C44" s="273" t="inlineStr">
+        <is>
+          <t>11:33:30</t>
+        </is>
+      </c>
+      <c r="D44" s="274" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E44" s="274" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F44" s="274" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H44" s="273" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I44" s="273" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" s="274" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION</t>
+        </is>
+      </c>
+      <c r="K44" s="273" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="L44" s="265" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M44" s="276" t="inlineStr">
+        <is>
+          <t>ALARM ACTIVE</t>
+        </is>
+      </c>
+      <c r="N44" s="273" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="O44" s="12" t="inlineStr">
+        <is>
+          <t>DISPATCH SECURITY — COORDINATED ENTRY</t>
+        </is>
+      </c>
+      <c r="P44" s="274" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q44" s="12" t="inlineStr">
+        <is>
+          <t>Ongoing — 41s elapsed</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="277" t="inlineStr">
+        <is>
+          <t>ALM-0002</t>
+        </is>
+      </c>
+      <c r="B45" s="278" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C45" s="278" t="inlineStr">
+        <is>
+          <t>11:33:38</t>
+        </is>
+      </c>
+      <c r="D45" s="279" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E45" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F45" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G45" s="18" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H45" s="278" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I45" s="278" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="279" t="inlineStr">
+        <is>
+          <t>CLEAR</t>
+        </is>
+      </c>
+      <c r="K45" s="278" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="265" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M45" s="221" t="inlineStr">
+        <is>
+          <t>SESSION ENDED</t>
+        </is>
+      </c>
+      <c r="N45" s="278" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="O45" s="18" t="inlineStr">
+        <is>
+          <t>NO ACTION REQUIRED</t>
+        </is>
+      </c>
+      <c r="P45" s="279" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q45" s="18" t="inlineStr">
+        <is>
+          <t>Session ended by operator</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="257" t="inlineStr">
+        <is>
+          <t>ALM-0001</t>
+        </is>
+      </c>
+      <c r="B46" s="258" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C46" s="258" t="inlineStr">
+        <is>
+          <t>11:56:36</t>
+        </is>
+      </c>
+      <c r="D46" s="259" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E46" s="259" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F46" s="259" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H46" s="258" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I46" s="258" t="n">
+        <v>2</v>
+      </c>
+      <c r="J46" s="259" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION</t>
+        </is>
+      </c>
+      <c r="K46" s="258" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="L46" s="265" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M46" s="261" t="inlineStr">
+        <is>
+          <t>ALARM RAISED</t>
+        </is>
+      </c>
+      <c r="N46" s="258" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="6" t="inlineStr">
+        <is>
+          <t>DISPATCH SECURITY — COORDINATED ENTRY</t>
+        </is>
+      </c>
+      <c r="P46" s="259" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>snapshots\ALM-0001_20260610_115636.jpg</t>
+        </is>
+      </c>
+      <c r="R46" s="259" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION — alarm triggered</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="277" t="inlineStr">
+        <is>
+          <t>ALM-0001</t>
+        </is>
+      </c>
+      <c r="B47" s="278" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C47" s="278" t="inlineStr">
+        <is>
+          <t>11:56:37</t>
+        </is>
+      </c>
+      <c r="D47" s="279" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E47" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F47" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G47" s="18" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H47" s="278" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I47" s="278" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" s="279" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION</t>
+        </is>
+      </c>
+      <c r="K47" s="278" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="L47" s="265" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M47" s="281" t="inlineStr">
+        <is>
+          <t>ALARM ACTIVE</t>
+        </is>
+      </c>
+      <c r="N47" s="278" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O47" s="18" t="inlineStr">
+        <is>
+          <t>DISPATCH SECURITY — COORDINATED ENTRY</t>
+        </is>
+      </c>
+      <c r="P47" s="279" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q47" s="18" t="inlineStr"/>
+      <c r="R47" s="279" t="inlineStr">
+        <is>
+          <t>Ongoing — 0s elapsed</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="272" t="inlineStr">
+        <is>
+          <t>ALM-0001</t>
+        </is>
+      </c>
+      <c r="B48" s="273" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C48" s="273" t="inlineStr">
+        <is>
+          <t>11:56:47</t>
+        </is>
+      </c>
+      <c r="D48" s="274" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E48" s="274" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F48" s="274" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H48" s="273" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I48" s="273" t="n">
+        <v>2</v>
+      </c>
+      <c r="J48" s="274" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION</t>
+        </is>
+      </c>
+      <c r="K48" s="273" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="L48" s="265" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M48" s="276" t="inlineStr">
+        <is>
+          <t>ALARM ACTIVE</t>
+        </is>
+      </c>
+      <c r="N48" s="273" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O48" s="12" t="inlineStr">
+        <is>
+          <t>DISPATCH SECURITY — COORDINATED ENTRY</t>
+        </is>
+      </c>
+      <c r="P48" s="274" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q48" s="12" t="inlineStr"/>
+      <c r="R48" s="274" t="inlineStr">
+        <is>
+          <t>Ongoing — 10s elapsed</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="277" t="inlineStr">
+        <is>
+          <t>ALM-0001</t>
+        </is>
+      </c>
+      <c r="B49" s="278" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C49" s="278" t="inlineStr">
+        <is>
+          <t>11:56:57</t>
+        </is>
+      </c>
+      <c r="D49" s="279" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E49" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F49" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G49" s="18" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H49" s="278" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I49" s="278" t="n">
+        <v>2</v>
+      </c>
+      <c r="J49" s="279" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION</t>
+        </is>
+      </c>
+      <c r="K49" s="278" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="L49" s="265" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M49" s="281" t="inlineStr">
+        <is>
+          <t>ALARM ACTIVE</t>
+        </is>
+      </c>
+      <c r="N49" s="278" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="O49" s="18" t="inlineStr">
+        <is>
+          <t>DISPATCH SECURITY — COORDINATED ENTRY</t>
+        </is>
+      </c>
+      <c r="P49" s="279" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q49" s="18" t="inlineStr"/>
+      <c r="R49" s="279" t="inlineStr">
+        <is>
+          <t>Ongoing — 21s elapsed</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="272" t="inlineStr">
+        <is>
+          <t>ALM-0001</t>
+        </is>
+      </c>
+      <c r="B50" s="273" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C50" s="273" t="inlineStr">
+        <is>
+          <t>11:57:07</t>
+        </is>
+      </c>
+      <c r="D50" s="274" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E50" s="274" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F50" s="274" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H50" s="273" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I50" s="273" t="n">
+        <v>2</v>
+      </c>
+      <c r="J50" s="274" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION</t>
+        </is>
+      </c>
+      <c r="K50" s="273" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="L50" s="265" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M50" s="276" t="inlineStr">
+        <is>
+          <t>ALARM ACTIVE</t>
+        </is>
+      </c>
+      <c r="N50" s="273" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="O50" s="12" t="inlineStr">
+        <is>
+          <t>DISPATCH SECURITY — COORDINATED ENTRY</t>
+        </is>
+      </c>
+      <c r="P50" s="274" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q50" s="12" t="inlineStr"/>
+      <c r="R50" s="274" t="inlineStr">
+        <is>
+          <t>Ongoing — 31s elapsed</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="277" t="inlineStr">
+        <is>
+          <t>ALM-0001</t>
+        </is>
+      </c>
+      <c r="B51" s="278" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C51" s="278" t="inlineStr">
+        <is>
+          <t>11:57:17</t>
+        </is>
+      </c>
+      <c r="D51" s="279" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E51" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F51" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G51" s="18" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H51" s="278" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I51" s="278" t="n">
+        <v>2</v>
+      </c>
+      <c r="J51" s="279" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION</t>
+        </is>
+      </c>
+      <c r="K51" s="278" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="L51" s="265" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M51" s="281" t="inlineStr">
+        <is>
+          <t>ALARM ACTIVE</t>
+        </is>
+      </c>
+      <c r="N51" s="278" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="O51" s="18" t="inlineStr">
+        <is>
+          <t>DISPATCH SECURITY — COORDINATED ENTRY</t>
+        </is>
+      </c>
+      <c r="P51" s="279" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q51" s="18" t="inlineStr"/>
+      <c r="R51" s="279" t="inlineStr">
+        <is>
+          <t>Ongoing — 41s elapsed</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="252" t="inlineStr">
+        <is>
+          <t>ALM-0001</t>
+        </is>
+      </c>
+      <c r="B52" s="253" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C52" s="253" t="inlineStr">
+        <is>
+          <t>11:57:23</t>
+        </is>
+      </c>
+      <c r="D52" s="254" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E52" s="254" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F52" s="254" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G52" s="34" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H52" s="253" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I52" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="254" t="inlineStr">
+        <is>
+          <t>CLEAR</t>
+        </is>
+      </c>
+      <c r="K52" s="253" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="265" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M52" s="256" t="inlineStr">
+        <is>
+          <t>ALARM CLEARED</t>
+        </is>
+      </c>
+      <c r="N52" s="253" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="O52" s="34" t="inlineStr">
+        <is>
+          <t>NO ACTION REQUIRED</t>
+        </is>
+      </c>
+      <c r="P52" s="254" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q52" s="34" t="inlineStr"/>
+      <c r="R52" s="254" t="inlineStr">
+        <is>
+          <t>Area clear after 47.2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="257" t="inlineStr">
+        <is>
+          <t>ALM-0002</t>
+        </is>
+      </c>
+      <c r="B53" s="258" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C53" s="258" t="inlineStr">
+        <is>
+          <t>11:57:24</t>
+        </is>
+      </c>
+      <c r="D53" s="259" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E53" s="259" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F53" s="259" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H53" s="258" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I53" s="258" t="n">
+        <v>2</v>
+      </c>
+      <c r="J53" s="259" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION</t>
+        </is>
+      </c>
+      <c r="K53" s="258" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="L53" s="265" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M53" s="261" t="inlineStr">
+        <is>
+          <t>ALARM RAISED</t>
+        </is>
+      </c>
+      <c r="N53" s="258" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="6" t="inlineStr">
+        <is>
+          <t>DISPATCH SECURITY — COORDINATED ENTRY</t>
+        </is>
+      </c>
+      <c r="P53" s="259" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>snapshots\ALM-0002_20260610_115724.jpg</t>
+        </is>
+      </c>
+      <c r="R53" s="259" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION — alarm triggered</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="272" t="inlineStr">
+        <is>
+          <t>ALM-0002</t>
+        </is>
+      </c>
+      <c r="B54" s="273" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C54" s="273" t="inlineStr">
+        <is>
+          <t>11:57:24</t>
+        </is>
+      </c>
+      <c r="D54" s="274" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E54" s="274" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F54" s="274" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H54" s="273" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I54" s="273" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" s="274" t="inlineStr">
+        <is>
+          <t>COORDINATED INTRUSION</t>
+        </is>
+      </c>
+      <c r="K54" s="273" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="L54" s="265" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M54" s="276" t="inlineStr">
+        <is>
+          <t>ALARM ACTIVE</t>
+        </is>
+      </c>
+      <c r="N54" s="273" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O54" s="12" t="inlineStr">
+        <is>
+          <t>DISPATCH SECURITY — COORDINATED ENTRY</t>
+        </is>
+      </c>
+      <c r="P54" s="274" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q54" s="12" t="inlineStr"/>
+      <c r="R54" s="274" t="inlineStr">
+        <is>
+          <t>Ongoing — 0s elapsed</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="277" t="inlineStr">
+        <is>
+          <t>ALM-0002</t>
+        </is>
+      </c>
+      <c r="B55" s="278" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C55" s="278" t="inlineStr">
+        <is>
+          <t>11:57:35</t>
+        </is>
+      </c>
+      <c r="D55" s="279" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E55" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F55" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G55" s="18" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H55" s="278" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I55" s="278" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" s="279" t="inlineStr">
+        <is>
+          <t>MASS INTRUSION</t>
+        </is>
+      </c>
+      <c r="K55" s="278" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="L55" s="280" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="M55" s="281" t="inlineStr">
+        <is>
+          <t>ALARM ACTIVE</t>
+        </is>
+      </c>
+      <c r="N55" s="278" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="O55" s="18" t="inlineStr">
+        <is>
+          <t>DISPATCH MULTIPLE UNITS — MASS INTRUSION</t>
+        </is>
+      </c>
+      <c r="P55" s="279" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q55" s="18" t="inlineStr"/>
+      <c r="R55" s="279" t="inlineStr">
+        <is>
+          <t>Ongoing — 11s elapsed</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="272" t="inlineStr">
+        <is>
+          <t>ALM-0002</t>
+        </is>
+      </c>
+      <c r="B56" s="273" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C56" s="273" t="inlineStr">
+        <is>
+          <t>11:57:45</t>
+        </is>
+      </c>
+      <c r="D56" s="274" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E56" s="274" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F56" s="274" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H56" s="273" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I56" s="273" t="n">
+        <v>3</v>
+      </c>
+      <c r="J56" s="274" t="inlineStr">
+        <is>
+          <t>MASS INTRUSION</t>
+        </is>
+      </c>
+      <c r="K56" s="273" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="L56" s="280" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="M56" s="276" t="inlineStr">
+        <is>
+          <t>ALARM ACTIVE</t>
+        </is>
+      </c>
+      <c r="N56" s="273" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="O56" s="12" t="inlineStr">
+        <is>
+          <t>DISPATCH MULTIPLE UNITS — MASS INTRUSION</t>
+        </is>
+      </c>
+      <c r="P56" s="274" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q56" s="12" t="inlineStr"/>
+      <c r="R56" s="274" t="inlineStr">
+        <is>
+          <t>Ongoing — 21s elapsed</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="277" t="inlineStr">
+        <is>
+          <t>ALM-0002</t>
+        </is>
+      </c>
+      <c r="B57" s="278" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C57" s="278" t="inlineStr">
+        <is>
+          <t>11:57:55</t>
+        </is>
+      </c>
+      <c r="D57" s="279" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E57" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F57" s="279" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G57" s="18" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H57" s="278" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I57" s="278" t="n">
+        <v>3</v>
+      </c>
+      <c r="J57" s="279" t="inlineStr">
+        <is>
+          <t>MASS INTRUSION</t>
+        </is>
+      </c>
+      <c r="K57" s="278" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="L57" s="280" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="M57" s="281" t="inlineStr">
+        <is>
+          <t>ALARM ACTIVE</t>
+        </is>
+      </c>
+      <c r="N57" s="278" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="O57" s="18" t="inlineStr">
+        <is>
+          <t>DISPATCH MULTIPLE UNITS — MASS INTRUSION</t>
+        </is>
+      </c>
+      <c r="P57" s="279" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q57" s="18" t="inlineStr"/>
+      <c r="R57" s="279" t="inlineStr">
+        <is>
+          <t>Ongoing — 31s elapsed</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="282" t="inlineStr">
+        <is>
+          <t>ALM-0002</t>
+        </is>
+      </c>
+      <c r="B58" s="283" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C58" s="283" t="inlineStr">
+        <is>
+          <t>11:58:00</t>
+        </is>
+      </c>
+      <c r="D58" s="284" t="inlineStr">
+        <is>
+          <t>AIRTEL-ASM-BTS-001</t>
+        </is>
+      </c>
+      <c r="E58" s="284" t="inlineStr">
+        <is>
+          <t>Guwahati North BTS</t>
+        </is>
+      </c>
+      <c r="F58" s="284" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam</t>
+        </is>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>RESTRICTED ZONE — AUTHORISED PERSONNEL ONLY</t>
+        </is>
+      </c>
+      <c r="H58" s="283" t="inlineStr">
+        <is>
+          <t>CAM-BTS-01</t>
+        </is>
+      </c>
+      <c r="I58" s="283" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="284" t="inlineStr">
+        <is>
+          <t>CLEAR</t>
+        </is>
+      </c>
+      <c r="K58" s="283" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="285" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M58" s="286" t="inlineStr">
+        <is>
+          <t>SESSION ENDED</t>
+        </is>
+      </c>
+      <c r="N58" s="283" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="O58" s="12" t="inlineStr">
+        <is>
+          <t>NO ACTION REQUIRED</t>
+        </is>
+      </c>
+      <c r="P58" s="284" t="inlineStr">
+        <is>
+          <t>NOC-OPS-ASM-01</t>
+        </is>
+      </c>
+      <c r="Q58" s="12" t="inlineStr"/>
+      <c r="R58" s="284" t="inlineStr">
         <is>
           <t>Session ended by operator</t>
         </is>
